--- a/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.116</v>
+        <v>0.0742</v>
       </c>
       <c r="E2">
-        <v>-0.164</v>
+        <v>0.29485</v>
       </c>
       <c r="G2">
-        <v>0.1982626248025358</v>
+        <v>0.2484972962883026</v>
       </c>
       <c r="H2">
-        <v>0.1982602500696933</v>
+        <v>0.248495312983066</v>
       </c>
       <c r="I2">
-        <v>0.1922697283512127</v>
+        <v>0.2439780436443817</v>
       </c>
       <c r="J2">
-        <v>0.1391379729439501</v>
+        <v>0.2032687474034635</v>
       </c>
       <c r="K2">
-        <v>796.92</v>
+        <v>634.9299999999999</v>
       </c>
       <c r="L2">
-        <v>0.08228139551691739</v>
+        <v>0.07407411728333847</v>
       </c>
       <c r="M2">
-        <v>761.4526</v>
+        <v>611.479</v>
       </c>
       <c r="N2">
-        <v>0.1003762994365922</v>
+        <v>0.08595960785890389</v>
       </c>
       <c r="O2">
-        <v>0.9554944034532952</v>
+        <v>0.9630652197880083</v>
       </c>
       <c r="P2">
-        <v>761.4526</v>
+        <v>611.471</v>
       </c>
       <c r="Q2">
-        <v>0.1003762994365922</v>
+        <v>0.08595848324650857</v>
       </c>
       <c r="R2">
-        <v>0.9554944034532952</v>
+        <v>0.9630526199738555</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.30830331049799e-05</v>
       </c>
       <c r="U2">
-        <v>2541.311</v>
+        <v>4976.813</v>
       </c>
       <c r="V2">
-        <v>0.3350010150303586</v>
+        <v>0.6996231986169517</v>
       </c>
       <c r="W2">
-        <v>0.1428571428571429</v>
+        <v>0.1427173195547766</v>
       </c>
       <c r="X2">
-        <v>0.07558878871651936</v>
+        <v>0.1375560562048306</v>
       </c>
       <c r="Y2">
-        <v>0.06726835414062352</v>
+        <v>0.00516126334994596</v>
       </c>
       <c r="Z2">
-        <v>1.034497859504909</v>
+        <v>1.061178308980786</v>
       </c>
       <c r="AA2">
-        <v>0.1457937170536623</v>
+        <v>0.1797588303307345</v>
       </c>
       <c r="AB2">
-        <v>0.05308523933287478</v>
+        <v>0.0872394212629117</v>
       </c>
       <c r="AC2">
-        <v>0.09270847772078747</v>
+        <v>0.0925194090678228</v>
       </c>
       <c r="AD2">
-        <v>6911.11</v>
+        <v>10258.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6911.11</v>
+        <v>10258.5</v>
       </c>
       <c r="AG2">
-        <v>4369.799</v>
+        <v>5281.687</v>
       </c>
       <c r="AH2">
-        <v>0.4767239494270919</v>
+        <v>0.5905171188083488</v>
       </c>
       <c r="AI2">
-        <v>0.396045113238676</v>
+        <v>0.5849922417317845</v>
       </c>
       <c r="AJ2">
-        <v>0.3654968028432108</v>
+        <v>0.42610576036028</v>
       </c>
       <c r="AK2">
-        <v>0.2930980812326837</v>
+        <v>0.4205393493929646</v>
       </c>
       <c r="AL2">
-        <v>104.439</v>
+        <v>604.501</v>
       </c>
       <c r="AM2">
-        <v>104.231</v>
+        <v>604.204</v>
       </c>
       <c r="AN2">
-        <v>3.435269732231175</v>
+        <v>4.650166587339362</v>
       </c>
       <c r="AO2">
-        <v>17.83040818085198</v>
+        <v>3.45949799917618</v>
       </c>
       <c r="AP2">
-        <v>2.172073406534414</v>
+        <v>2.39418281543936</v>
       </c>
       <c r="AQ2">
-        <v>17.86598996459787</v>
+        <v>3.461198535593939</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Europejskie Centrum Odszkodowan S.A. (WSE:EUC)</t>
+          <t>Votum S.A. (WSE:VOT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.106</v>
+        <v>0.211</v>
       </c>
       <c r="E3">
-        <v>-0.237</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2587786259541985</v>
+        <v>0.1065139442231076</v>
       </c>
       <c r="H3">
-        <v>0.2587786259541985</v>
+        <v>0.1061752988047809</v>
       </c>
       <c r="I3">
-        <v>0.2053435114503817</v>
+        <v>0.3426294820717131</v>
       </c>
       <c r="J3">
-        <v>0.1751686198616636</v>
+        <v>0.2753420054720875</v>
       </c>
       <c r="K3">
-        <v>1.8</v>
+        <v>13.1</v>
       </c>
       <c r="L3">
-        <v>0.1374045801526718</v>
+        <v>0.2609561752988048</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.879</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.006851130163678877</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.06709923664122137</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.871</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.006788776305533904</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.06648854961832061</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.008000000000000007</v>
+      </c>
+      <c r="T3">
+        <v>0.009101251422070543</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="V3">
-        <v>0.3393574297188754</v>
+        <v>0.01270459859703819</v>
       </c>
       <c r="W3">
-        <v>0.1428571428571429</v>
+        <v>0.8343949044585988</v>
       </c>
       <c r="X3">
-        <v>0.1148153301426955</v>
+        <v>0.0854424502774649</v>
       </c>
       <c r="Y3">
-        <v>0.02804181271444736</v>
+        <v>0.7489524541811339</v>
       </c>
       <c r="Z3">
-        <v>1.021044427123929</v>
+        <v>2.991835031885095</v>
       </c>
       <c r="AA3">
-        <v>0.1788549431167415</v>
+        <v>0.823777857720889</v>
       </c>
       <c r="AB3">
-        <v>0.05457994052077551</v>
+        <v>0.08415293146701529</v>
       </c>
       <c r="AC3">
-        <v>0.124275002595966</v>
+        <v>0.7396249262538737</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AG3">
-        <v>9.81</v>
+        <v>3.67</v>
       </c>
       <c r="AH3">
-        <v>0.6978155339805825</v>
+        <v>0.03967065868263472</v>
       </c>
       <c r="AI3">
-        <v>0.4323308270676692</v>
+        <v>0.1766666666666667</v>
       </c>
       <c r="AJ3">
-        <v>0.6632860040567952</v>
+        <v>0.02780935060998712</v>
       </c>
       <c r="AK3">
-        <v>0.3938177438779607</v>
+        <v>0.1293620021149101</v>
       </c>
       <c r="AL3">
-        <v>0.761</v>
+        <v>0.202</v>
       </c>
       <c r="AM3">
-        <v>0.5840000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="AN3">
-        <v>3.709677419354839</v>
+        <v>0.3011363636363636</v>
       </c>
       <c r="AO3">
-        <v>3.534822601839684</v>
+        <v>85.14851485148515</v>
       </c>
       <c r="AP3">
-        <v>3.164516129032258</v>
+        <v>0.2085227272727272</v>
       </c>
       <c r="AQ3">
-        <v>4.606164383561643</v>
+        <v>109.5541401273885</v>
       </c>
     </row>
     <row r="4">
@@ -853,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.116</v>
+        <v>0.0742</v>
       </c>
       <c r="E4">
-        <v>0.116</v>
+        <v>0.0247</v>
       </c>
       <c r="G4">
-        <v>0.1987762183276369</v>
+        <v>0.2500264236474029</v>
       </c>
       <c r="H4">
-        <v>0.1987762183276369</v>
+        <v>0.2500264236474029</v>
       </c>
       <c r="I4">
-        <v>0.1929481918573848</v>
+        <v>0.2441192704724548</v>
       </c>
       <c r="J4">
-        <v>0.1413635170476165</v>
+        <v>0.1698621832380346</v>
       </c>
       <c r="K4">
-        <v>793.8</v>
+        <v>627</v>
       </c>
       <c r="L4">
-        <v>0.08246501625822</v>
+        <v>0.0736338974292727</v>
       </c>
       <c r="M4">
-        <v>761.4305999999999</v>
+        <v>610.6</v>
       </c>
       <c r="N4">
-        <v>0.1010994622585142</v>
+        <v>0.08742465243474651</v>
       </c>
       <c r="O4">
-        <v>0.9592222222222222</v>
+        <v>0.9738437001594896</v>
       </c>
       <c r="P4">
-        <v>761.4305999999999</v>
+        <v>610.6</v>
       </c>
       <c r="Q4">
-        <v>0.1010994622585142</v>
+        <v>0.08742465243474651</v>
       </c>
       <c r="R4">
-        <v>0.9592222222222222</v>
+        <v>0.9738437001594896</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2538.7</v>
+        <v>4975.1</v>
       </c>
       <c r="V4">
-        <v>0.3370776073823276</v>
+        <v>0.7123262173732514</v>
       </c>
       <c r="W4">
-        <v>0.1712695261931475</v>
+        <v>0.1427173195547766</v>
       </c>
       <c r="X4">
-        <v>0.07558878871651936</v>
+        <v>0.1375560562048306</v>
       </c>
       <c r="Y4">
-        <v>0.09568073747662811</v>
+        <v>0.00516126334994596</v>
       </c>
       <c r="Z4">
-        <v>1.031339061863844</v>
+        <v>1.058262804021725</v>
       </c>
       <c r="AA4">
-        <v>0.1457937170536623</v>
+        <v>0.1797588303307345</v>
       </c>
       <c r="AB4">
-        <v>0.05308523933287478</v>
+        <v>0.0872394212629117</v>
       </c>
       <c r="AC4">
-        <v>0.09270847772078747</v>
+        <v>0.0925194090678228</v>
       </c>
       <c r="AD4">
-        <v>6892.5</v>
+        <v>10244.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6892.5</v>
+        <v>10244.9</v>
       </c>
       <c r="AG4">
-        <v>4353.8</v>
+        <v>5269.799999999999</v>
       </c>
       <c r="AH4">
-        <v>0.4778494176372712</v>
+        <v>0.5946242425649478</v>
       </c>
       <c r="AI4">
-        <v>0.3961002017137044</v>
+        <v>0.5857207379753132</v>
       </c>
       <c r="AJ4">
-        <v>0.3663180567591899</v>
+        <v>0.4300438220677161</v>
       </c>
       <c r="AK4">
-        <v>0.2929445169624955</v>
+        <v>0.42104506232023</v>
       </c>
       <c r="AL4">
-        <v>103.5</v>
+        <v>603.5</v>
       </c>
       <c r="AM4">
-        <v>103.5</v>
+        <v>603.5</v>
       </c>
       <c r="AN4">
-        <v>3.435942173479561</v>
+        <v>4.671850061562314</v>
       </c>
       <c r="AO4">
-        <v>17.94492753623188</v>
+        <v>3.444407622203811</v>
       </c>
       <c r="AP4">
-        <v>2.170388833499501</v>
+        <v>2.403119157280313</v>
       </c>
       <c r="AQ4">
-        <v>17.94492753623188</v>
+        <v>3.444407622203811</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Votum S.A. (WSE:VOT)</t>
+          <t>Europejskie Centrum Odszkodowan S.A. (WSE:EUC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,121 +990,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.137</v>
-      </c>
-      <c r="E5">
-        <v>-0.164</v>
+        <v>-0.193</v>
       </c>
       <c r="G5">
-        <v>0.07436285097192225</v>
+        <v>-0.6944</v>
       </c>
       <c r="H5">
-        <v>0.07386609071274298</v>
+        <v>-0.6944</v>
       </c>
       <c r="I5">
-        <v>0.04751619870410368</v>
+        <v>-0.7408</v>
       </c>
       <c r="J5">
-        <v>0.02781024218570129</v>
+        <v>-0.7408</v>
       </c>
       <c r="K5">
-        <v>1.32</v>
+        <v>-5.17</v>
       </c>
       <c r="L5">
-        <v>0.02850971922246221</v>
+        <v>-0.8271999999999999</v>
       </c>
       <c r="M5">
-        <v>0.022</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0004444444444444444</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.022</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0004444444444444444</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.01666666666666667</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0.921</v>
+        <v>0.083</v>
       </c>
       <c r="V5">
-        <v>0.01860606060606061</v>
+        <v>0.08627858627858628</v>
       </c>
       <c r="W5">
-        <v>0.0830188679245283</v>
+        <v>-0.3493243243243243</v>
       </c>
       <c r="X5">
-        <v>0.05387981410671015</v>
+        <v>0.3993422930315225</v>
       </c>
       <c r="Y5">
-        <v>0.02913905381781815</v>
+        <v>-0.7486666173558468</v>
       </c>
       <c r="Z5">
-        <v>2.877563704164076</v>
+        <v>0.4367575122292104</v>
       </c>
       <c r="AA5">
-        <v>0.08002574351758666</v>
+        <v>-0.323549965059399</v>
       </c>
       <c r="AB5">
-        <v>0.05069162828547874</v>
+        <v>0.08891633463624614</v>
       </c>
       <c r="AC5">
-        <v>0.02933411523210792</v>
+        <v>-0.4124662996956452</v>
       </c>
       <c r="AD5">
-        <v>7.11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>7.11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AG5">
-        <v>6.189</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.1255961844197138</v>
+        <v>0.8961347441157418</v>
       </c>
       <c r="AI5">
-        <v>0.3117053923717668</v>
+        <v>0.552228875582169</v>
       </c>
       <c r="AJ5">
-        <v>0.1111350536012498</v>
+        <v>0.8951955550713586</v>
       </c>
       <c r="AK5">
-        <v>0.2827447576408242</v>
+        <v>0.5497424232287416</v>
       </c>
       <c r="AL5">
-        <v>0.178</v>
+        <v>0.799</v>
       </c>
       <c r="AM5">
-        <v>0.147</v>
+        <v>0.547</v>
       </c>
       <c r="AN5">
-        <v>2.623616236162362</v>
+        <v>-1.865168539325843</v>
       </c>
       <c r="AO5">
-        <v>12.35955056179775</v>
+        <v>-5.794743429286608</v>
       </c>
       <c r="AP5">
-        <v>2.283763837638376</v>
+        <v>-1.846516853932584</v>
       </c>
       <c r="AQ5">
-        <v>14.96598639455783</v>
+        <v>-8.46435100548446</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0742</v>
+        <v>0.091</v>
       </c>
       <c r="E2">
-        <v>0.29485</v>
+        <v>0.50705</v>
       </c>
       <c r="G2">
-        <v>0.2484972962883026</v>
+        <v>0.226593234206782</v>
       </c>
       <c r="H2">
-        <v>0.248495312983066</v>
+        <v>0.2265918053646254</v>
       </c>
       <c r="I2">
-        <v>0.2439780436443817</v>
+        <v>0.4124766497110731</v>
       </c>
       <c r="J2">
-        <v>0.2032687474034635</v>
+        <v>0.3525576562625012</v>
       </c>
       <c r="K2">
-        <v>634.9299999999999</v>
+        <v>1141.1</v>
       </c>
       <c r="L2">
-        <v>0.07407411728333847</v>
+        <v>0.08581325183418212</v>
       </c>
       <c r="M2">
-        <v>611.479</v>
+        <v>858.9</v>
       </c>
       <c r="N2">
-        <v>0.08595960785890389</v>
+        <v>0.08162821536429478</v>
       </c>
       <c r="O2">
-        <v>0.9630652197880083</v>
+        <v>0.7526947682061168</v>
       </c>
       <c r="P2">
-        <v>611.471</v>
+        <v>858.9</v>
       </c>
       <c r="Q2">
-        <v>0.08595848324650857</v>
+        <v>0.08162821536429478</v>
       </c>
       <c r="R2">
-        <v>0.9630526199738555</v>
+        <v>0.7526947682061168</v>
       </c>
       <c r="S2">
-        <v>0.008000000000000007</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1.30830331049799e-05</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>4976.813</v>
+        <v>3426.469</v>
       </c>
       <c r="V2">
-        <v>0.6996231986169517</v>
+        <v>0.3256450686588425</v>
       </c>
       <c r="W2">
-        <v>0.1427173195547766</v>
+        <v>0.3616777883698761</v>
       </c>
       <c r="X2">
-        <v>0.1375560562048306</v>
+        <v>0.1011268370210035</v>
       </c>
       <c r="Y2">
-        <v>0.00516126334994596</v>
+        <v>0.2605509513488726</v>
       </c>
       <c r="Z2">
-        <v>1.061178308980786</v>
+        <v>1.687609469511746</v>
       </c>
       <c r="AA2">
-        <v>0.1797588303307345</v>
+        <v>0.5256825334826518</v>
       </c>
       <c r="AB2">
-        <v>0.0872394212629117</v>
+        <v>0.07652383443413802</v>
       </c>
       <c r="AC2">
-        <v>0.0925194090678228</v>
+        <v>0.4491586990485138</v>
       </c>
       <c r="AD2">
-        <v>10258.5</v>
+        <v>9180.809999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10258.5</v>
+        <v>9180.809999999999</v>
       </c>
       <c r="AG2">
-        <v>5281.687</v>
+        <v>5754.340999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5905171188083488</v>
+        <v>0.4659622054755677</v>
       </c>
       <c r="AI2">
-        <v>0.5849922417317845</v>
+        <v>0.4122203109698849</v>
       </c>
       <c r="AJ2">
-        <v>0.42610576036028</v>
+        <v>0.3535381021326656</v>
       </c>
       <c r="AK2">
-        <v>0.4205393493929646</v>
+        <v>0.3053487899082315</v>
       </c>
       <c r="AL2">
-        <v>604.501</v>
+        <v>2283.57</v>
       </c>
       <c r="AM2">
-        <v>604.204</v>
+        <v>2283.357</v>
       </c>
       <c r="AN2">
-        <v>4.650166587339362</v>
+        <v>1.637442034672184</v>
       </c>
       <c r="AO2">
-        <v>3.45949799917618</v>
+        <v>2.401897029650941</v>
       </c>
       <c r="AP2">
-        <v>2.39418281543936</v>
+        <v>1.026314653634872</v>
       </c>
       <c r="AQ2">
-        <v>3.461198535593939</v>
+        <v>2.402121087504057</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.211</v>
+        <v>0.286</v>
       </c>
       <c r="E3">
-        <v>0.5649999999999999</v>
+        <v>0.922</v>
       </c>
       <c r="G3">
-        <v>0.1065139442231076</v>
+        <v>0.3088578371810449</v>
       </c>
       <c r="H3">
-        <v>0.1061752988047809</v>
+        <v>0.3086269744835966</v>
       </c>
       <c r="I3">
-        <v>0.3426294820717131</v>
+        <v>0.3730255164034022</v>
       </c>
       <c r="J3">
-        <v>0.2753420054720875</v>
+        <v>0.3022520951643277</v>
       </c>
       <c r="K3">
-        <v>13.1</v>
+        <v>26.5</v>
       </c>
       <c r="L3">
-        <v>0.2609561752988048</v>
+        <v>0.321992709599028</v>
       </c>
       <c r="M3">
-        <v>0.879</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>0.006851130163678877</v>
+        <v>0.007834757834757835</v>
       </c>
       <c r="O3">
-        <v>0.06709923664122137</v>
+        <v>0.04150943396226416</v>
       </c>
       <c r="P3">
-        <v>0.871</v>
+        <v>1.1</v>
       </c>
       <c r="Q3">
-        <v>0.006788776305533904</v>
+        <v>0.007834757834757835</v>
       </c>
       <c r="R3">
-        <v>0.06648854961832061</v>
+        <v>0.04150943396226416</v>
       </c>
       <c r="S3">
-        <v>0.008000000000000007</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.009101251422070543</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>4.41</v>
       </c>
       <c r="V3">
-        <v>0.01270459859703819</v>
+        <v>0.03141025641025641</v>
       </c>
       <c r="W3">
-        <v>0.8343949044585988</v>
+        <v>1.081632653061225</v>
       </c>
       <c r="X3">
-        <v>0.0854424502774649</v>
+        <v>0.07631170076540578</v>
       </c>
       <c r="Y3">
-        <v>0.7489524541811339</v>
+        <v>1.005320952295819</v>
       </c>
       <c r="Z3">
-        <v>2.991835031885095</v>
+        <v>3.345528455284553</v>
       </c>
       <c r="AA3">
-        <v>0.823777857720889</v>
+        <v>1.011192985041633</v>
       </c>
       <c r="AB3">
-        <v>0.08415293146701529</v>
+        <v>0.07525109200920856</v>
       </c>
       <c r="AC3">
-        <v>0.7396249262538737</v>
+        <v>0.9359418930324243</v>
       </c>
       <c r="AD3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AG3">
-        <v>3.67</v>
+        <v>1.19</v>
       </c>
       <c r="AH3">
-        <v>0.03967065868263472</v>
+        <v>0.03835616438356164</v>
       </c>
       <c r="AI3">
-        <v>0.1766666666666667</v>
+        <v>0.1046728971962617</v>
       </c>
       <c r="AJ3">
-        <v>0.02780935060998712</v>
+        <v>0.008404548343809588</v>
       </c>
       <c r="AK3">
-        <v>0.1293620021149101</v>
+        <v>0.02424118965166021</v>
       </c>
       <c r="AL3">
-        <v>0.202</v>
+        <v>0.575</v>
       </c>
       <c r="AM3">
-        <v>0.157</v>
+        <v>0.393</v>
       </c>
       <c r="AN3">
-        <v>0.3011363636363636</v>
+        <v>0.178343949044586</v>
       </c>
       <c r="AO3">
-        <v>85.14851485148515</v>
+        <v>53.39130434782609</v>
       </c>
       <c r="AP3">
-        <v>0.2085227272727272</v>
+        <v>0.03789808917197451</v>
       </c>
       <c r="AQ3">
-        <v>109.5541401273885</v>
+        <v>78.11704834605598</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0742</v>
+        <v>0.091</v>
       </c>
       <c r="E4">
-        <v>0.0247</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="G4">
-        <v>0.2500264236474029</v>
+        <v>0.2273838630806846</v>
       </c>
       <c r="H4">
-        <v>0.2500264236474029</v>
+        <v>0.2273838630806846</v>
       </c>
       <c r="I4">
-        <v>0.2441192704724548</v>
+        <v>0.4141415670630625</v>
       </c>
       <c r="J4">
-        <v>0.1698621832380346</v>
+        <v>0.3122333083958439</v>
       </c>
       <c r="K4">
-        <v>627</v>
+        <v>1138.2</v>
       </c>
       <c r="L4">
-        <v>0.0736338974292727</v>
+        <v>0.08615743298992483</v>
       </c>
       <c r="M4">
-        <v>610.6</v>
+        <v>857.8</v>
       </c>
       <c r="N4">
-        <v>0.08742465243474651</v>
+        <v>0.08263332305795315</v>
       </c>
       <c r="O4">
-        <v>0.9738437001594896</v>
+        <v>0.7536461078896503</v>
       </c>
       <c r="P4">
-        <v>610.6</v>
+        <v>857.8</v>
       </c>
       <c r="Q4">
-        <v>0.08742465243474651</v>
+        <v>0.08263332305795315</v>
       </c>
       <c r="R4">
-        <v>0.9738437001594896</v>
+        <v>0.7536461078896503</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4975.1</v>
+        <v>3421.5</v>
       </c>
       <c r="V4">
-        <v>0.7123262173732514</v>
+        <v>0.3295988748458693</v>
       </c>
       <c r="W4">
-        <v>0.1427173195547766</v>
+        <v>0.3616777883698761</v>
       </c>
       <c r="X4">
-        <v>0.1375560562048306</v>
+        <v>0.1011268370210035</v>
       </c>
       <c r="Y4">
-        <v>0.00516126334994596</v>
+        <v>0.2605509513488726</v>
       </c>
       <c r="Z4">
-        <v>1.058262804021725</v>
+        <v>1.683620931358805</v>
       </c>
       <c r="AA4">
-        <v>0.1797588303307345</v>
+        <v>0.5256825334826518</v>
       </c>
       <c r="AB4">
-        <v>0.0872394212629117</v>
+        <v>0.07652383443413802</v>
       </c>
       <c r="AC4">
-        <v>0.0925194090678228</v>
+        <v>0.4491586990485138</v>
       </c>
       <c r="AD4">
-        <v>10244.9</v>
+        <v>9166</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10244.9</v>
+        <v>9166</v>
       </c>
       <c r="AG4">
-        <v>5269.799999999999</v>
+        <v>5744.5</v>
       </c>
       <c r="AH4">
-        <v>0.5946242425649478</v>
+        <v>0.4689258599873125</v>
       </c>
       <c r="AI4">
-        <v>0.5857207379753132</v>
+        <v>0.4123479450082775</v>
       </c>
       <c r="AJ4">
-        <v>0.4300438220677161</v>
+        <v>0.3562414342678896</v>
       </c>
       <c r="AK4">
-        <v>0.42104506232023</v>
+        <v>0.3054399089715164</v>
       </c>
       <c r="AL4">
-        <v>603.5</v>
+        <v>2282.9</v>
       </c>
       <c r="AM4">
-        <v>603.5</v>
+        <v>2282.9</v>
       </c>
       <c r="AN4">
-        <v>4.671850061562314</v>
+        <v>1.639068702836093</v>
       </c>
       <c r="AO4">
-        <v>3.444407622203811</v>
+        <v>2.396557010819572</v>
       </c>
       <c r="AP4">
-        <v>2.403119157280313</v>
+        <v>1.027234362147277</v>
       </c>
       <c r="AQ4">
-        <v>3.444407622203811</v>
+        <v>2.396557010819572</v>
       </c>
     </row>
     <row r="5">
@@ -990,25 +990,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.193</v>
+        <v>-0.273</v>
       </c>
       <c r="G5">
-        <v>-0.6944</v>
+        <v>-3.616071428571428</v>
       </c>
       <c r="H5">
-        <v>-0.6944</v>
+        <v>-3.616071428571428</v>
       </c>
       <c r="I5">
-        <v>-0.7408</v>
+        <v>-3.772321428571428</v>
       </c>
       <c r="J5">
-        <v>-0.7408</v>
+        <v>-3.772321428571428</v>
       </c>
       <c r="K5">
-        <v>-5.17</v>
+        <v>-23.6</v>
       </c>
       <c r="L5">
-        <v>-0.8271999999999999</v>
+        <v>-5.267857142857142</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1032,73 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.083</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="V5">
-        <v>0.08627858627858628</v>
+        <v>0.6231884057971014</v>
       </c>
       <c r="W5">
-        <v>-0.3493243243243243</v>
+        <v>-3.527653213751869</v>
       </c>
       <c r="X5">
-        <v>0.3993422930315225</v>
+        <v>0.3773483859981561</v>
       </c>
       <c r="Y5">
-        <v>-0.7486666173558468</v>
+        <v>-3.905001599750025</v>
       </c>
       <c r="Z5">
-        <v>0.4367575122292104</v>
+        <v>0.5412589102331763</v>
       </c>
       <c r="AA5">
-        <v>-0.323549965059399</v>
+        <v>-2.04180258547783</v>
       </c>
       <c r="AB5">
-        <v>0.08891633463624614</v>
+        <v>0.09554675220982542</v>
       </c>
       <c r="AC5">
-        <v>-0.4124662996956452</v>
+        <v>-2.137349337687655</v>
       </c>
       <c r="AD5">
-        <v>8.300000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8.300000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AG5">
-        <v>8.217000000000001</v>
+        <v>8.651000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.8961347441157418</v>
+        <v>0.9112496289700207</v>
       </c>
       <c r="AI5">
-        <v>0.552228875582169</v>
+        <v>-0.8615528531337702</v>
       </c>
       <c r="AJ5">
-        <v>0.8951955550713586</v>
+        <v>0.9060536237955593</v>
       </c>
       <c r="AK5">
-        <v>0.5497424232287416</v>
+        <v>-0.7690461374344389</v>
       </c>
       <c r="AL5">
-        <v>0.799</v>
+        <v>0.095</v>
       </c>
       <c r="AM5">
-        <v>0.547</v>
+        <v>0.064</v>
       </c>
       <c r="AN5">
-        <v>-1.865168539325843</v>
+        <v>-0.5482142857142858</v>
       </c>
       <c r="AO5">
-        <v>-5.794743429286608</v>
+        <v>-177.8947368421053</v>
       </c>
       <c r="AP5">
-        <v>-1.846516853932584</v>
+        <v>-0.5149404761904762</v>
       </c>
       <c r="AQ5">
-        <v>-8.46435100548446</v>
+        <v>-264.0625</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.091</v>
+        <v>0.0698</v>
       </c>
       <c r="E2">
-        <v>0.50705</v>
+        <v>0.108</v>
       </c>
       <c r="G2">
-        <v>0.226593234206782</v>
+        <v>0.4330272004790512</v>
       </c>
       <c r="H2">
-        <v>0.2265918053646254</v>
+        <v>0.4330272004790512</v>
       </c>
       <c r="I2">
-        <v>0.4124766497110731</v>
+        <v>0.4060545311350781</v>
       </c>
       <c r="J2">
-        <v>0.3525576562625012</v>
+        <v>0.3149343840254182</v>
       </c>
       <c r="K2">
-        <v>1141.1</v>
+        <v>1369</v>
       </c>
       <c r="L2">
-        <v>0.08581325183418212</v>
+        <v>0.08910613979705409</v>
       </c>
       <c r="M2">
-        <v>858.9</v>
+        <v>975.7549999999999</v>
       </c>
       <c r="N2">
-        <v>0.08162821536429478</v>
+        <v>0.1018799269120334</v>
       </c>
       <c r="O2">
-        <v>0.7526947682061168</v>
+        <v>0.7127501826150474</v>
       </c>
       <c r="P2">
-        <v>858.9</v>
+        <v>975.7549999999999</v>
       </c>
       <c r="Q2">
-        <v>0.08162821536429478</v>
+        <v>0.1018799269120334</v>
       </c>
       <c r="R2">
-        <v>0.7526947682061168</v>
+        <v>0.7127501826150474</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3426.469</v>
+        <v>6226.8</v>
       </c>
       <c r="V2">
-        <v>0.3256450686588425</v>
+        <v>0.6501487862176978</v>
       </c>
       <c r="W2">
-        <v>0.3616777883698761</v>
+        <v>0.2085173789868096</v>
       </c>
       <c r="X2">
-        <v>0.1011268370210035</v>
+        <v>0.1112735910221859</v>
       </c>
       <c r="Y2">
-        <v>0.2605509513488726</v>
+        <v>0.09724378796462377</v>
       </c>
       <c r="Z2">
-        <v>1.687609469511746</v>
+        <v>1.317562410489936</v>
       </c>
       <c r="AA2">
-        <v>0.5256825334826518</v>
+        <v>0.4149457061626934</v>
       </c>
       <c r="AB2">
-        <v>0.07652383443413802</v>
+        <v>0.07943861160798141</v>
       </c>
       <c r="AC2">
-        <v>0.4491586990485138</v>
+        <v>0.3355070945547121</v>
       </c>
       <c r="AD2">
-        <v>9180.809999999999</v>
+        <v>10945.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9180.809999999999</v>
+        <v>10945.2</v>
       </c>
       <c r="AG2">
-        <v>5754.340999999999</v>
+        <v>4718.400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4659622054755677</v>
+        <v>0.5333216389656332</v>
       </c>
       <c r="AI2">
-        <v>0.4122203109698849</v>
+        <v>0.4035305048002478</v>
       </c>
       <c r="AJ2">
-        <v>0.3535381021326656</v>
+        <v>0.3300526724445471</v>
       </c>
       <c r="AK2">
-        <v>0.3053487899082315</v>
+        <v>0.225795337085104</v>
       </c>
       <c r="AL2">
-        <v>2283.57</v>
+        <v>2145.5</v>
       </c>
       <c r="AM2">
-        <v>2283.357</v>
+        <v>2145.5</v>
       </c>
       <c r="AN2">
-        <v>1.637442034672184</v>
+        <v>1.654028077916975</v>
       </c>
       <c r="AO2">
-        <v>2.401897029650941</v>
+        <v>2.907713819622466</v>
       </c>
       <c r="AP2">
-        <v>1.026314653634872</v>
+        <v>0.713040061656567</v>
       </c>
       <c r="AQ2">
-        <v>2.402121087504057</v>
+        <v>2.907713819622466</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Votum S.A. (WSE:VOT)</t>
+          <t>Powszechny Zaklad Ubezpieczen SA (WSE:PZU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.286</v>
+        <v>0.0698</v>
       </c>
       <c r="E3">
-        <v>0.922</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
-        <v>0.3088578371810449</v>
+        <v>0.4330272004790512</v>
       </c>
       <c r="H3">
-        <v>0.3086269744835966</v>
+        <v>0.4330272004790512</v>
       </c>
       <c r="I3">
-        <v>0.3730255164034022</v>
+        <v>0.4060545311350781</v>
       </c>
       <c r="J3">
-        <v>0.3022520951643277</v>
+        <v>0.3149343840254182</v>
       </c>
       <c r="K3">
-        <v>26.5</v>
+        <v>1369</v>
       </c>
       <c r="L3">
-        <v>0.321992709599028</v>
+        <v>0.08910613979705409</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>975.7549999999999</v>
       </c>
       <c r="N3">
-        <v>0.007834757834757835</v>
+        <v>0.1018799269120334</v>
       </c>
       <c r="O3">
-        <v>0.04150943396226416</v>
+        <v>0.7127501826150474</v>
       </c>
       <c r="P3">
-        <v>1.1</v>
+        <v>975.7549999999999</v>
       </c>
       <c r="Q3">
-        <v>0.007834757834757835</v>
+        <v>0.1018799269120334</v>
       </c>
       <c r="R3">
-        <v>0.04150943396226416</v>
+        <v>0.7127501826150474</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,335 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.41</v>
+        <v>6226.8</v>
       </c>
       <c r="V3">
-        <v>0.03141025641025641</v>
+        <v>0.6501487862176978</v>
       </c>
       <c r="W3">
-        <v>1.081632653061225</v>
+        <v>0.2085173789868096</v>
       </c>
       <c r="X3">
-        <v>0.07631170076540578</v>
+        <v>0.1112735910221859</v>
       </c>
       <c r="Y3">
-        <v>1.005320952295819</v>
+        <v>0.09724378796462377</v>
       </c>
       <c r="Z3">
-        <v>3.345528455284553</v>
+        <v>1.317562410489936</v>
       </c>
       <c r="AA3">
-        <v>1.011192985041633</v>
+        <v>0.4149457061626934</v>
       </c>
       <c r="AB3">
-        <v>0.07525109200920856</v>
+        <v>0.07943861160798141</v>
       </c>
       <c r="AC3">
-        <v>0.9359418930324243</v>
+        <v>0.3355070945547121</v>
       </c>
       <c r="AD3">
-        <v>5.6</v>
+        <v>10945.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.6</v>
+        <v>10945.2</v>
       </c>
       <c r="AG3">
-        <v>1.19</v>
+        <v>4718.400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.03835616438356164</v>
+        <v>0.5333216389656332</v>
       </c>
       <c r="AI3">
-        <v>0.1046728971962617</v>
+        <v>0.4035305048002478</v>
       </c>
       <c r="AJ3">
-        <v>0.008404548343809588</v>
+        <v>0.3300526724445471</v>
       </c>
       <c r="AK3">
-        <v>0.02424118965166021</v>
+        <v>0.225795337085104</v>
       </c>
       <c r="AL3">
-        <v>0.575</v>
+        <v>2145.5</v>
       </c>
       <c r="AM3">
-        <v>0.393</v>
+        <v>2145.5</v>
       </c>
       <c r="AN3">
-        <v>0.178343949044586</v>
+        <v>1.654028077916975</v>
       </c>
       <c r="AO3">
-        <v>53.39130434782609</v>
+        <v>2.907713819622466</v>
       </c>
       <c r="AP3">
-        <v>0.03789808917197451</v>
+        <v>0.713040061656567</v>
       </c>
       <c r="AQ3">
-        <v>78.11704834605598</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Powszechny Zaklad Ubezpieczen SA (WSE:PZU)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.091</v>
-      </c>
-      <c r="E4">
-        <v>0.09210000000000002</v>
-      </c>
-      <c r="G4">
-        <v>0.2273838630806846</v>
-      </c>
-      <c r="H4">
-        <v>0.2273838630806846</v>
-      </c>
-      <c r="I4">
-        <v>0.4141415670630625</v>
-      </c>
-      <c r="J4">
-        <v>0.3122333083958439</v>
-      </c>
-      <c r="K4">
-        <v>1138.2</v>
-      </c>
-      <c r="L4">
-        <v>0.08615743298992483</v>
-      </c>
-      <c r="M4">
-        <v>857.8</v>
-      </c>
-      <c r="N4">
-        <v>0.08263332305795315</v>
-      </c>
-      <c r="O4">
-        <v>0.7536461078896503</v>
-      </c>
-      <c r="P4">
-        <v>857.8</v>
-      </c>
-      <c r="Q4">
-        <v>0.08263332305795315</v>
-      </c>
-      <c r="R4">
-        <v>0.7536461078896503</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>3421.5</v>
-      </c>
-      <c r="V4">
-        <v>0.3295988748458693</v>
-      </c>
-      <c r="W4">
-        <v>0.3616777883698761</v>
-      </c>
-      <c r="X4">
-        <v>0.1011268370210035</v>
-      </c>
-      <c r="Y4">
-        <v>0.2605509513488726</v>
-      </c>
-      <c r="Z4">
-        <v>1.683620931358805</v>
-      </c>
-      <c r="AA4">
-        <v>0.5256825334826518</v>
-      </c>
-      <c r="AB4">
-        <v>0.07652383443413802</v>
-      </c>
-      <c r="AC4">
-        <v>0.4491586990485138</v>
-      </c>
-      <c r="AD4">
-        <v>9166</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>9166</v>
-      </c>
-      <c r="AG4">
-        <v>5744.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.4689258599873125</v>
-      </c>
-      <c r="AI4">
-        <v>0.4123479450082775</v>
-      </c>
-      <c r="AJ4">
-        <v>0.3562414342678896</v>
-      </c>
-      <c r="AK4">
-        <v>0.3054399089715164</v>
-      </c>
-      <c r="AL4">
-        <v>2282.9</v>
-      </c>
-      <c r="AM4">
-        <v>2282.9</v>
-      </c>
-      <c r="AN4">
-        <v>1.639068702836093</v>
-      </c>
-      <c r="AO4">
-        <v>2.396557010819572</v>
-      </c>
-      <c r="AP4">
-        <v>1.027234362147277</v>
-      </c>
-      <c r="AQ4">
-        <v>2.396557010819572</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Europejskie Centrum Odszkodowan S.A. (WSE:EUC)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.273</v>
-      </c>
-      <c r="G5">
-        <v>-3.616071428571428</v>
-      </c>
-      <c r="H5">
-        <v>-3.616071428571428</v>
-      </c>
-      <c r="I5">
-        <v>-3.772321428571428</v>
-      </c>
-      <c r="J5">
-        <v>-3.772321428571428</v>
-      </c>
-      <c r="K5">
-        <v>-23.6</v>
-      </c>
-      <c r="L5">
-        <v>-5.267857142857142</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="V5">
-        <v>0.6231884057971014</v>
-      </c>
-      <c r="W5">
-        <v>-3.527653213751869</v>
-      </c>
-      <c r="X5">
-        <v>0.3773483859981561</v>
-      </c>
-      <c r="Y5">
-        <v>-3.905001599750025</v>
-      </c>
-      <c r="Z5">
-        <v>0.5412589102331763</v>
-      </c>
-      <c r="AA5">
-        <v>-2.04180258547783</v>
-      </c>
-      <c r="AB5">
-        <v>0.09554675220982542</v>
-      </c>
-      <c r="AC5">
-        <v>-2.137349337687655</v>
-      </c>
-      <c r="AD5">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="AG5">
-        <v>8.651000000000002</v>
-      </c>
-      <c r="AH5">
-        <v>0.9112496289700207</v>
-      </c>
-      <c r="AI5">
-        <v>-0.8615528531337702</v>
-      </c>
-      <c r="AJ5">
-        <v>0.9060536237955593</v>
-      </c>
-      <c r="AK5">
-        <v>-0.7690461374344389</v>
-      </c>
-      <c r="AL5">
-        <v>0.095</v>
-      </c>
-      <c r="AM5">
-        <v>0.064</v>
-      </c>
-      <c r="AN5">
-        <v>-0.5482142857142858</v>
-      </c>
-      <c r="AO5">
-        <v>-177.8947368421053</v>
-      </c>
-      <c r="AP5">
-        <v>-0.5149404761904762</v>
-      </c>
-      <c r="AQ5">
-        <v>-264.0625</v>
+        <v>2.907713819622466</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0698</v>
+        <v>0.1589</v>
       </c>
       <c r="E2">
-        <v>0.108</v>
+        <v>0.273</v>
       </c>
       <c r="G2">
-        <v>0.4330272004790512</v>
+        <v>0.4329820488612408</v>
       </c>
       <c r="H2">
-        <v>0.4330272004790512</v>
+        <v>0.4329806908860465</v>
       </c>
       <c r="I2">
-        <v>0.4060545311350781</v>
+        <v>0.4054784599267987</v>
       </c>
       <c r="J2">
-        <v>0.3149343840254182</v>
+        <v>0.3212007735377876</v>
       </c>
       <c r="K2">
-        <v>1369</v>
+        <v>1395.4</v>
       </c>
       <c r="L2">
-        <v>0.08910613979705409</v>
+        <v>0.09023421838827744</v>
       </c>
       <c r="M2">
-        <v>975.7549999999999</v>
+        <v>983.6549999999999</v>
       </c>
       <c r="N2">
-        <v>0.1018799269120334</v>
+        <v>0.1017423278617308</v>
       </c>
       <c r="O2">
-        <v>0.7127501826150474</v>
+        <v>0.7049269026802349</v>
       </c>
       <c r="P2">
-        <v>975.7549999999999</v>
+        <v>983.6549999999999</v>
       </c>
       <c r="Q2">
-        <v>0.1018799269120334</v>
+        <v>0.1017423278617308</v>
       </c>
       <c r="R2">
-        <v>0.7127501826150474</v>
+        <v>0.7049269026802349</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6226.8</v>
+        <v>6234.22</v>
       </c>
       <c r="V2">
-        <v>0.6501487862176978</v>
+        <v>0.6448236985550418</v>
       </c>
       <c r="W2">
-        <v>0.2085173789868096</v>
+        <v>0.3827397021516327</v>
       </c>
       <c r="X2">
-        <v>0.1112735910221859</v>
+        <v>0.09644337964361024</v>
       </c>
       <c r="Y2">
-        <v>0.09724378796462377</v>
+        <v>0.2862963225080224</v>
       </c>
       <c r="Z2">
-        <v>1.317562410489936</v>
+        <v>1.321085148406586</v>
       </c>
       <c r="AA2">
-        <v>0.4149457061626934</v>
+        <v>0.4942426152846349</v>
       </c>
       <c r="AB2">
-        <v>0.07943861160798141</v>
+        <v>0.07958497658673824</v>
       </c>
       <c r="AC2">
-        <v>0.3355070945547121</v>
+        <v>0.4146576386978966</v>
       </c>
       <c r="AD2">
-        <v>10945.2</v>
+        <v>10951.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10945.2</v>
+        <v>10951.3</v>
       </c>
       <c r="AG2">
-        <v>4718.400000000001</v>
+        <v>4717.080000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5333216389656332</v>
+        <v>0.5311163273422117</v>
       </c>
       <c r="AI2">
-        <v>0.4035305048002478</v>
+        <v>0.402536968355896</v>
       </c>
       <c r="AJ2">
-        <v>0.3300526724445471</v>
+        <v>0.3279124765904911</v>
       </c>
       <c r="AK2">
-        <v>0.225795337085104</v>
+        <v>0.2249283312384248</v>
       </c>
       <c r="AL2">
-        <v>2145.5</v>
+        <v>2146.033</v>
       </c>
       <c r="AM2">
-        <v>2145.5</v>
+        <v>2145.805</v>
       </c>
       <c r="AN2">
-        <v>1.654028077916975</v>
+        <v>1.646737741154535</v>
       </c>
       <c r="AO2">
-        <v>2.907713819622466</v>
+        <v>2.921856280868001</v>
       </c>
       <c r="AP2">
-        <v>0.713040061656567</v>
+        <v>0.7093033396989611</v>
       </c>
       <c r="AQ2">
-        <v>2.907713819622466</v>
+        <v>2.922166739288985</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Powszechny Zaklad Ubezpieczen SA (WSE:PZU)</t>
+          <t>Votum S.A. (WSE:VOT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0698</v>
+        <v>0.248</v>
       </c>
       <c r="E3">
-        <v>0.108</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G3">
-        <v>0.4330272004790512</v>
+        <v>0.4260796019900497</v>
       </c>
       <c r="H3">
-        <v>0.4330272004790512</v>
+        <v>0.4258706467661691</v>
       </c>
       <c r="I3">
-        <v>0.4060545311350781</v>
+        <v>0.317412935323383</v>
       </c>
       <c r="J3">
-        <v>0.3149343840254182</v>
+        <v>0.256694605052814</v>
       </c>
       <c r="K3">
-        <v>1369</v>
+        <v>26.4</v>
       </c>
       <c r="L3">
-        <v>0.08910613979705409</v>
+        <v>0.2626865671641791</v>
       </c>
       <c r="M3">
-        <v>975.7549999999999</v>
+        <v>7.9</v>
       </c>
       <c r="N3">
-        <v>0.1018799269120334</v>
+        <v>0.08719646799116999</v>
       </c>
       <c r="O3">
-        <v>0.7127501826150474</v>
+        <v>0.2992424242424243</v>
       </c>
       <c r="P3">
-        <v>975.7549999999999</v>
+        <v>7.9</v>
       </c>
       <c r="Q3">
-        <v>0.1018799269120334</v>
+        <v>0.08719646799116999</v>
       </c>
       <c r="R3">
-        <v>0.7127501826150474</v>
+        <v>0.2992424242424243</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,72 +770,206 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6226.8</v>
+        <v>7.42</v>
       </c>
       <c r="V3">
-        <v>0.6501487862176978</v>
+        <v>0.08189845474613687</v>
       </c>
       <c r="W3">
-        <v>0.2085173789868096</v>
+        <v>0.5569620253164557</v>
       </c>
       <c r="X3">
-        <v>0.1112735910221859</v>
+        <v>0.08163998333817039</v>
       </c>
       <c r="Y3">
-        <v>0.09724378796462377</v>
+        <v>0.4753220419782853</v>
       </c>
       <c r="Z3">
-        <v>1.317562410489936</v>
+        <v>2.234326367274344</v>
       </c>
       <c r="AA3">
-        <v>0.4149457061626934</v>
+        <v>0.5735395244065764</v>
       </c>
       <c r="AB3">
-        <v>0.07943861160798141</v>
+        <v>0.07974385557987711</v>
       </c>
       <c r="AC3">
-        <v>0.3355070945547121</v>
+        <v>0.4937956688266993</v>
       </c>
       <c r="AD3">
-        <v>10945.2</v>
+        <v>6.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
+        <v>6.1</v>
+      </c>
+      <c r="AG3">
+        <v>-1.32</v>
+      </c>
+      <c r="AH3">
+        <v>0.06308169596690796</v>
+      </c>
+      <c r="AI3">
+        <v>0.07429963459196103</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.01478494623655914</v>
+      </c>
+      <c r="AK3">
+        <v>-0.01767541510444564</v>
+      </c>
+      <c r="AL3">
+        <v>0.533</v>
+      </c>
+      <c r="AM3">
+        <v>0.305</v>
+      </c>
+      <c r="AN3">
+        <v>0.1848484848484848</v>
+      </c>
+      <c r="AO3">
+        <v>59.8499061913696</v>
+      </c>
+      <c r="AP3">
+        <v>-0.04000000000000001</v>
+      </c>
+      <c r="AQ3">
+        <v>104.5901639344262</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Powszechny Zaklad Ubezpieczen SA (WSE:PZU)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0698</v>
+      </c>
+      <c r="E4">
+        <v>0.108</v>
+      </c>
+      <c r="G4">
+        <v>0.4330272004790512</v>
+      </c>
+      <c r="H4">
+        <v>0.4330272004790512</v>
+      </c>
+      <c r="I4">
+        <v>0.4060545311350781</v>
+      </c>
+      <c r="J4">
+        <v>0.3149343840254182</v>
+      </c>
+      <c r="K4">
+        <v>1369</v>
+      </c>
+      <c r="L4">
+        <v>0.08910613979705409</v>
+      </c>
+      <c r="M4">
+        <v>975.7549999999999</v>
+      </c>
+      <c r="N4">
+        <v>0.1018799269120334</v>
+      </c>
+      <c r="O4">
+        <v>0.7127501826150474</v>
+      </c>
+      <c r="P4">
+        <v>975.7549999999999</v>
+      </c>
+      <c r="Q4">
+        <v>0.1018799269120334</v>
+      </c>
+      <c r="R4">
+        <v>0.7127501826150474</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>6226.8</v>
+      </c>
+      <c r="V4">
+        <v>0.6501487862176978</v>
+      </c>
+      <c r="W4">
+        <v>0.2085173789868096</v>
+      </c>
+      <c r="X4">
+        <v>0.1112467759490501</v>
+      </c>
+      <c r="Y4">
+        <v>0.09727060303775953</v>
+      </c>
+      <c r="Z4">
+        <v>1.317562410489936</v>
+      </c>
+      <c r="AA4">
+        <v>0.4149457061626934</v>
+      </c>
+      <c r="AB4">
+        <v>0.07942609759359939</v>
+      </c>
+      <c r="AC4">
+        <v>0.335519608569094</v>
+      </c>
+      <c r="AD4">
         <v>10945.2</v>
       </c>
-      <c r="AG3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>10945.2</v>
+      </c>
+      <c r="AG4">
         <v>4718.400000000001</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.5333216389656332</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.4035305048002478</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.3300526724445471</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.225795337085104</v>
       </c>
-      <c r="AL3">
+      <c r="AL4">
         <v>2145.5</v>
       </c>
-      <c r="AM3">
+      <c r="AM4">
         <v>2145.5</v>
       </c>
-      <c r="AN3">
+      <c r="AN4">
         <v>1.654028077916975</v>
       </c>
-      <c r="AO3">
+      <c r="AO4">
         <v>2.907713819622466</v>
       </c>
-      <c r="AP3">
+      <c r="AP4">
         <v>0.713040061656567</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ4">
         <v>2.907713819622466</v>
       </c>
     </row>
